--- a/Commit2_audit.xlsx
+++ b/Commit2_audit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a832f6e089c31e67/Desktop/RegAnProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_284D8FE7BC9456D4AC151C962E101A939CBE2D1B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E6BBE95-6C9A-4152-8C4A-B5FD8FB57123}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_284D8FE7E4C41C807E1604962E101A939CBE2D7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF2BDE8-19C6-4DF3-8CCA-0D68F7BEEFE0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="224">
   <si>
     <t>variable</t>
   </si>
@@ -77,24 +77,24 @@
     <t>workout_id</t>
   </si>
   <si>
+    <t>workout_date_time</t>
+  </si>
+  <si>
+    <t>workout_date</t>
+  </si>
+  <si>
+    <t>workout_time</t>
+  </si>
+  <si>
+    <t>workout_team_id</t>
+  </si>
+  <si>
+    <t>workout_name</t>
+  </si>
+  <si>
     <t>Predictor candidate</t>
   </si>
   <si>
-    <t>workout_date_time</t>
-  </si>
-  <si>
-    <t>workout_date</t>
-  </si>
-  <si>
-    <t>workout_time</t>
-  </si>
-  <si>
-    <t>workout_team_id</t>
-  </si>
-  <si>
-    <t>workout_name</t>
-  </si>
-  <si>
     <t>workout_text</t>
   </si>
   <si>
@@ -693,9 +693,6 @@
   </si>
   <si>
     <t>y</t>
-  </si>
-  <si>
-    <t>n</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1039,7 @@
   <dimension ref="A1:M191"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1214,15 +1211,15 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1249,15 +1246,15 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1292,7 +1289,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1327,7 +1324,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1354,15 +1351,15 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1389,7 +1386,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -1421,7 +1421,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -1453,7 +1456,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="M12" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1485,7 +1491,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="M13" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1689,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -1945,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -2009,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -2041,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -2073,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -2393,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
@@ -2425,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
@@ -3225,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
@@ -3257,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
@@ -4668,7 +4677,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>131</v>
       </c>
@@ -4700,7 +4709,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>132</v>
       </c>
@@ -4732,7 +4741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>133</v>
       </c>
@@ -4764,7 +4773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>134</v>
       </c>
@@ -4795,11 +4804,8 @@
       <c r="J116" t="s">
         <v>46</v>
       </c>
-      <c r="M116" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>135</v>
       </c>
@@ -4830,11 +4836,8 @@
       <c r="J117" t="s">
         <v>46</v>
       </c>
-      <c r="M117" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>136</v>
       </c>
@@ -4865,11 +4868,8 @@
       <c r="J118" t="s">
         <v>46</v>
       </c>
-      <c r="M118" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>137</v>
       </c>
@@ -4900,11 +4900,8 @@
       <c r="J119" t="s">
         <v>46</v>
       </c>
-      <c r="M119" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>138</v>
       </c>
@@ -4935,11 +4932,8 @@
       <c r="J120" t="s">
         <v>46</v>
       </c>
-      <c r="M120" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>139</v>
       </c>
@@ -4970,11 +4964,8 @@
       <c r="J121" t="s">
         <v>46</v>
       </c>
-      <c r="M121" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>140</v>
       </c>
@@ -5005,11 +4996,8 @@
       <c r="J122" t="s">
         <v>46</v>
       </c>
-      <c r="M122" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>141</v>
       </c>
@@ -5040,11 +5028,8 @@
       <c r="J123" t="s">
         <v>46</v>
       </c>
-      <c r="M123" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>142</v>
       </c>
@@ -5075,11 +5060,8 @@
       <c r="J124" t="s">
         <v>46</v>
       </c>
-      <c r="M124" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>143</v>
       </c>
@@ -5110,11 +5092,8 @@
       <c r="J125" t="s">
         <v>46</v>
       </c>
-      <c r="M125" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>144</v>
       </c>
@@ -5145,11 +5124,8 @@
       <c r="J126" t="s">
         <v>46</v>
       </c>
-      <c r="M126" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>145</v>
       </c>
@@ -5180,11 +5156,8 @@
       <c r="J127" t="s">
         <v>46</v>
       </c>
-      <c r="M127" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>146</v>
       </c>
@@ -5215,11 +5188,8 @@
       <c r="J128" t="s">
         <v>37</v>
       </c>
-      <c r="M128" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>147</v>
       </c>
@@ -5250,11 +5220,8 @@
       <c r="J129" t="s">
         <v>46</v>
       </c>
-      <c r="M129" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>148</v>
       </c>
@@ -5285,11 +5252,8 @@
       <c r="J130" t="s">
         <v>46</v>
       </c>
-      <c r="M130" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>149</v>
       </c>
@@ -5320,11 +5284,8 @@
       <c r="J131" t="s">
         <v>46</v>
       </c>
-      <c r="M131" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>150</v>
       </c>
@@ -5355,11 +5316,8 @@
       <c r="J132" t="s">
         <v>46</v>
       </c>
-      <c r="M132" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>151</v>
       </c>
@@ -5390,11 +5348,8 @@
       <c r="J133" t="s">
         <v>37</v>
       </c>
-      <c r="M133" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>152</v>
       </c>
@@ -5425,11 +5380,8 @@
       <c r="J134" t="s">
         <v>46</v>
       </c>
-      <c r="M134" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>153</v>
       </c>
@@ -5460,11 +5412,8 @@
       <c r="J135" t="s">
         <v>46</v>
       </c>
-      <c r="M135" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -5495,11 +5444,8 @@
       <c r="J136" t="s">
         <v>46</v>
       </c>
-      <c r="M136" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>155</v>
       </c>
@@ -5530,11 +5476,8 @@
       <c r="J137" t="s">
         <v>46</v>
       </c>
-      <c r="M137" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>156</v>
       </c>
@@ -5565,11 +5508,8 @@
       <c r="J138" t="s">
         <v>46</v>
       </c>
-      <c r="M138" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>157</v>
       </c>
@@ -5600,11 +5540,8 @@
       <c r="J139" t="s">
         <v>37</v>
       </c>
-      <c r="M139" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>158</v>
       </c>
@@ -5635,11 +5572,8 @@
       <c r="J140" t="s">
         <v>37</v>
       </c>
-      <c r="M140" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>159</v>
       </c>
@@ -5670,11 +5604,8 @@
       <c r="J141" t="s">
         <v>37</v>
       </c>
-      <c r="M141" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>160</v>
       </c>
@@ -5705,11 +5636,8 @@
       <c r="J142" t="s">
         <v>46</v>
       </c>
-      <c r="M142" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>161</v>
       </c>
@@ -5740,11 +5668,8 @@
       <c r="J143" t="s">
         <v>46</v>
       </c>
-      <c r="M143" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>162</v>
       </c>
@@ -5775,11 +5700,8 @@
       <c r="J144" t="s">
         <v>46</v>
       </c>
-      <c r="M144" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>163</v>
       </c>
@@ -5810,11 +5732,8 @@
       <c r="J145" t="s">
         <v>37</v>
       </c>
-      <c r="M145" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -5845,11 +5764,8 @@
       <c r="J146" t="s">
         <v>46</v>
       </c>
-      <c r="M146" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -5880,11 +5796,8 @@
       <c r="J147" t="s">
         <v>37</v>
       </c>
-      <c r="M147" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>166</v>
       </c>
@@ -5915,11 +5828,8 @@
       <c r="J148" t="s">
         <v>37</v>
       </c>
-      <c r="M148" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -5950,11 +5860,8 @@
       <c r="J149" t="s">
         <v>37</v>
       </c>
-      <c r="M149" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>168</v>
       </c>
@@ -5985,11 +5892,8 @@
       <c r="J150" t="s">
         <v>46</v>
       </c>
-      <c r="M150" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>169</v>
       </c>
@@ -6020,11 +5924,8 @@
       <c r="J151" t="s">
         <v>46</v>
       </c>
-      <c r="M151" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>170</v>
       </c>
@@ -6055,11 +5956,8 @@
       <c r="J152" t="s">
         <v>46</v>
       </c>
-      <c r="M152" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>171</v>
       </c>
@@ -6090,11 +5988,8 @@
       <c r="J153" t="s">
         <v>46</v>
       </c>
-      <c r="M153" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>172</v>
       </c>
@@ -6125,11 +6020,8 @@
       <c r="J154" t="s">
         <v>46</v>
       </c>
-      <c r="M154" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>173</v>
       </c>
@@ -6160,11 +6052,8 @@
       <c r="J155" t="s">
         <v>46</v>
       </c>
-      <c r="M155" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>174</v>
       </c>
@@ -6195,11 +6084,8 @@
       <c r="J156" t="s">
         <v>46</v>
       </c>
-      <c r="M156" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>175</v>
       </c>
@@ -6230,11 +6116,8 @@
       <c r="J157" t="s">
         <v>46</v>
       </c>
-      <c r="M157" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>176</v>
       </c>
@@ -6265,11 +6148,8 @@
       <c r="J158" t="s">
         <v>46</v>
       </c>
-      <c r="M158" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>177</v>
       </c>
@@ -6300,11 +6180,8 @@
       <c r="J159" t="s">
         <v>46</v>
       </c>
-      <c r="M159" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>178</v>
       </c>
@@ -6335,11 +6212,8 @@
       <c r="J160" t="s">
         <v>46</v>
       </c>
-      <c r="M160" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>179</v>
       </c>
@@ -6370,11 +6244,8 @@
       <c r="J161" t="s">
         <v>46</v>
       </c>
-      <c r="M161" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>180</v>
       </c>
@@ -6405,11 +6276,8 @@
       <c r="J162" t="s">
         <v>46</v>
       </c>
-      <c r="M162" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>181</v>
       </c>
@@ -6440,11 +6308,8 @@
       <c r="J163" t="s">
         <v>37</v>
       </c>
-      <c r="M163" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>182</v>
       </c>
@@ -6475,11 +6340,8 @@
       <c r="J164" t="s">
         <v>37</v>
       </c>
-      <c r="M164" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>183</v>
       </c>
@@ -6510,11 +6372,8 @@
       <c r="J165" t="s">
         <v>37</v>
       </c>
-      <c r="M165" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>184</v>
       </c>
@@ -6545,11 +6404,8 @@
       <c r="J166" t="s">
         <v>37</v>
       </c>
-      <c r="M166" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>185</v>
       </c>
@@ -6580,11 +6436,8 @@
       <c r="J167" t="s">
         <v>37</v>
       </c>
-      <c r="M167" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>186</v>
       </c>
@@ -6615,11 +6468,8 @@
       <c r="J168" t="s">
         <v>37</v>
       </c>
-      <c r="M168" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>187</v>
       </c>
@@ -6651,7 +6501,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>188</v>
       </c>
@@ -6683,7 +6533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>189</v>
       </c>
@@ -6715,7 +6565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>190</v>
       </c>
@@ -6747,7 +6597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>191</v>
       </c>
@@ -6779,7 +6629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>192</v>
       </c>
@@ -6811,7 +6661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>193</v>
       </c>
@@ -6843,7 +6693,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>194</v>
       </c>
@@ -7224,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="J187" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M187" t="s">
         <v>223</v>
@@ -7259,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M188" t="s">
         <v>223</v>
